--- a/Assessment Questions/CDE/DATA ENGINEERING ASSOCIATE/DATA ENGINEERING PROJECT/Data Pipeline setup/etl_pipeline_questions.xlsx
+++ b/Assessment Questions/CDE/DATA ENGINEERING ASSOCIATE/DATA ENGINEERING PROJECT/Data Pipeline setup/etl_pipeline_questions.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ETL Pipeline" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -434,12 +434,12 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Correct Answer</t>
+          <t>Explanation</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Explanation</t>
+          <t>Question Type</t>
         </is>
       </c>
     </row>
@@ -454,15 +454,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Extract Transform Load</t>
+          <t>ETL stands for Extract, Transform, Load.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ETL stands for Extract, Transform, Load.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -477,15 +476,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Transform location</t>
+          <t>ETL transforms before loading; ELT transforms after loading.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ETL transforms before loading; ELT transforms after loading.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -500,15 +498,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Pandas</t>
+          <t>Pandas provides read_csv, read_sql, and other extraction tools.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Pandas provides read_csv, read_sql, and other extraction tools.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -523,15 +520,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Data retrieval</t>
+          <t>APIs provide programmatic access to data sources.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>APIs provide programmatic access to data sources.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -546,15 +542,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Snowflake is a popular cloud data warehouse.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Snowflake is a popular cloud data warehouse.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -569,15 +564,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Quality assurance</t>
+          <t>Validation ensures data meets quality standards.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Validation ensures data meets quality standards.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -599,12 +593,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Data quality checks identify and handle missing records.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data quality checks identify and handle missing records.</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
@@ -619,15 +613,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Repeatable safe</t>
+          <t>Idempotent pipelines produce same result regardless of reruns.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Idempotent pipelines produce same result regardless of reruns.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -642,15 +635,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Structure</t>
+          <t>Schemas define table structures and relationships.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Schemas define table structures and relationships.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -665,15 +657,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Efficiency</t>
+          <t>Only new or changed data is processed.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Only new or changed data is processed.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -688,15 +679,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Track changes</t>
+          <t>CDC captures inserts, updates, and deletes.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CDC captures inserts, updates, and deletes.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -711,15 +701,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Airflow</t>
+          <t>Apache Airflow schedules and monitors pipelines.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Apache Airflow schedules and monitors pipelines.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -734,15 +723,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Intermediate storage</t>
+          <t>Staging holds raw data before transformation.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Staging holds raw data before transformation.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -757,15 +745,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Data segmentation</t>
+          <t>Partitioning splits data for better performance.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Partitioning splits data for better performance.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -787,12 +774,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Proper error handling captures and logs failures.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Proper error handling captures and logs failures.</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
@@ -807,15 +794,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Metadata management</t>
+          <t>Data catalogs track data lineage and definitions.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data catalogs track data lineage and definitions.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -830,15 +816,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Parquet</t>
+          <t>Parquet provides efficient columnar storage.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Parquet provides efficient columnar storage.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -853,15 +838,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Historical processing</t>
+          <t>Backfill processes data for past time periods.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Backfill processes data for past time periods.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -876,15 +860,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Data tracking</t>
+          <t>Lineage shows data origin and transformations.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lineage shows data origin and transformations.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -906,12 +889,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Lambda architecture handles both batch and stream processing.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lambda architecture handles both batch and stream processing.</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
